--- a/SS_mapping.xlsx
+++ b/SS_mapping.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>

--- a/SS_mapping.xlsx
+++ b/SS_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,8 +765,14 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>64165163150001</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -799,56 +805,34 @@
       <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>64265165900006</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>64165163290002</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>DEV032399</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>mst_devices_ELS-MST ELS device presence</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>reset_button-reset_test-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NV: what is the RC?</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -867,10 +851,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>64265165900007</v>
+        <v>64265165900006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -878,11 +862,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>64165163290001</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+        <v>64165163290002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>64165163150005</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
@@ -891,9 +885,21 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>mst_devices_ELS-MST ELS device presence</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -907,52 +913,34 @@
       <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>64265165900008</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>64165163290003</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>DEV032399</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
+          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NV: what is the RC?</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -971,10 +959,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>64165163330007</v>
+        <v>64265165900007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -982,9 +970,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64165163290005</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>64165163290001</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -995,9 +987,21 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,8,6,16,8,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,9,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,10,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,11,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,7,16,12,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,13,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,14,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,15,64,0,31.89,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1010,6 +1014,156 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>64265165900008</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>64165163290003</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>64165163150002</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DEV032399</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NV: what is the RC?</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>64165163330007</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>64165163290005</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DEV032399</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SS_mapping.xlsx
+++ b/SS_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>HS_COLD</t>
+          <t>HS_HOT</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -845,59 +845,31 @@
       <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>64265165900006</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>64165163290002</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>64165163150005</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>DEV032399</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>mst_devices_ELS-MST ELS device presence</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,0,13,0,49,129.31,12.86,8.26,6.73,-12.6,nan],[prp:-12.6,7,0,13,0,49,129.31,12.86,8.26,6.73,-12.6,nan],[prb:nan,7,0,13,1,49,129.31,12.73,8.39,6.73,-12.6,nan],[prp:-12.6,7,0,13,1,49,129.31,12.73,8.39,6.73,-12.6,nan],[prb:nan,7,0,13,2,49,129.31,12.98,8.14,6.73,-12.91,nan],[prp:-12.91,7,0,13,2,49,129.31,12.98,8.14,6.73,-12.91,nan],[prb:nan,7,0,13,3,49,129.31,12.89,8.23,6.86,-10.61,nan],[prp:-10.61,7,0,13,3,49,129.31,12.89,8.23,6.86,-10.61,nan],[prb:nan,7,2,13,8,51,109.38,12.98,7.41,7.11,-18.93,nan],[prp:-18.93,7,2,13,8,51,109.38,12.98,7.41,7.11,-18.93,nan],[prb:nan,7,2,13,9,51,109.38,13.09,7.3,6.99,-19.47,nan],[prp:-19.47,7,2,13,9,51,109.38,13.09,7.3,6.99,-19.47,nan],[prb:nan,7,2,13,10,51,109.38,13.09,7.3,6.99,-20.09,nan],[prp:-20.09,7,2,13,10,51,109.38,13.09,7.3,6.99,-20.09,nan],[prb:nan,7,2,13,11,51,109.38,12.98,7.41,6.86,-19.91,nan],[prp:-19.91,7,2,13,11,51,109.38,12.98,7.41,6.86,-19.91,nan],[prb:nan,7,3,13,12,52,124.04,12.82,8.12,6.73,-17.12,nan],[prp:-17.12,7,3,13,12,52,124.04,12.82,8.12,6.73,-17.12,nan],[prb:nan,7,3,13,13,52,124.04,12.92,8.02,6.86,-17.21,nan],[prp:-17.21,7,3,13,13,52,124.04,12.92,8.02,6.86,-17.21,nan],[prb:nan,7,3,13,14,52,124.04,12.89,8.05,6.73,-19.07,nan],[prp:-19.07,7,3,13,14,52,124.04,12.89,8.05,6.73,-19.07,nan],[prb:nan,7,3,13,15,52,124.04,12.73,8.21,6.6,-19.47,nan],[prp:-19.47,7,3,13,15,52,124.04,12.73,8.21,6.6,-19.47,nan],[prb:nan,5,2,9,8,35,114.81,12.95,7.65,6.86,-19.21,nan],[prp:-19.21,5,2,9,8,35,114.81,12.95,7.65,6.86,-19.21,nan],[prb:nan,5,2,9,9,35,114.81,13.01,7.59,6.86,-19.47,nan],[prp:-19.47,5,2,9,9,35,114.81,13.01,7.59,6.86,-19.47,nan],[prb:nan,5,2,9,10,35,114.81,13.07,7.53,6.99,-18.93,nan],[prp:-18.93,5,2,9,10,35,114.81,13.07,7.53,6.99,-18.93,nan],[prb:nan,5,2,9,11,35,114.81,12.89,7.71,6.73,-18.57,nan],[prp:-18.57,5,2,9,11,35,114.81,12.89,7.71,6.73,-18.57,nan],[prb:nan,5,3,9,12,36,134.62,12.89,8.4,6.73,-12.16,nan],[prp:-12.16,5,3,9,12,36,134.62,12.89,8.4,6.73,-12.16,nan],[prb:nan,5,3,9,13,36,134.62,12.95,8.34,6.73,-12.4,nan],[prp:-12.4,5,3,9,13,36,134.62,12.95,8.34,6.73,-12.4,nan],[prb:nan,5,3,9,14,36,134.62,12.95,8.34,6.6,-12.16,nan],[prp:-12.16,5,3,9,14,36,134.62,12.95,8.34,6.6,-12.16,nan],[prb:nan,5,3,9,15,36,134.62,12.82,8.47,6.73,-12.57,nan],[prp:-12.57,5,3,9,15,36,134.62,12.82,8.47,6.73,-12.57,nan],[prb:nan,5,0,9,0,33,124.28,12.89,8.05,6.73,-19.07,nan],[prp:-19.07,5,0,9,0,33,124.28,12.89,8.05,6.73,-19.07,nan],[prb:nan,5,0,9,1,33,124.28,12.73,8.21,6.6,-18.93,nan],[prp:-18.93,5,0,9,1,33,124.28,12.73,8.21,6.6,-18.93,nan],[prb:nan,5,0,9,2,33,124.28,12.82,8.12,6.73,-18.36,nan],[prp:-18.36,5,0,9,2,33,124.28,12.82,8.12,6.73,-18.36,nan],[prb:nan,5,0,9,3,33,124.28,12.86,8.08,6.73,-18.36,nan],[prp:-18.36,5,0,9,3,33,124.28,12.86,8.08,6.73,-18.36,nan],[prb:nan,5,1,9,4,34,124.63,12.95,8.01,6.86,-12.97,nan],[prp:-12.97,5,1,9,4,34,124.63,12.95,8.01,6.86,-12.97,nan],[prb:nan,5,1,9,5,34,124.63,12.82,8.14,6.73,-15.5,nan],[prp:-15.5,5,1,9,5,34,124.63,12.82,8.14,6.73,-15.5,nan],[prb:nan,5,1,9,6,34,124.63,12.92,8.04,6.73,-13.2,nan],[prp:-13.2,5,1,9,6,34,124.63,12.92,8.04,6.73,-13.2,nan],[prb:nan,5,1,9,7,34,124.63,12.89,8.07,6.73,-15.13,nan],[prp:-15.13,5,1,9,7,34,124.63,12.89,8.07,6.73,-15.13,nan],[prb:nan,3,2,5,8,19,129.33,12.7,8.42,6.6,-18.48,nan],[prp:-18.48,3,2,5,8,19,129.33,12.7,8.42,6.6,-18.48,nan],[prb:nan,3,2,5,9,19,129.33,12.73,8.39,6.6,-18.15,nan],[prp:-18.15,3,2,5,9,19,129.33,12.73,8.39,6.6,-18.15,nan],[prb:nan,3,2,5,10,19,129.33,12.73,8.39,6.6,-21.61,nan],[prp:-21.61,3,2,5,10,19,129.33,12.73,8.39,6.6,-21.61,nan],[prb:nan,3,2,5,11,19,129.33,12.54,8.58,6.46,-22.37,nan],[prp:-22.37,3,2,5,11,19,129.33,12.54,8.58,6.46,-22.37,nan],[prb:nan,3,3,5,12,20,134.86,12.67,8.63,6.6,-19.75,nan],[prp:-19.75,3,3,5,12,20,134.86,12.67,8.63,6.6,-19.75,nan],[prb:nan,3,3,5,13,20,134.86,12.82,8.48,6.73,-19.47,nan],[prp:-19.47,3,3,5,13,20,134.86,12.82,8.48,6.73,-19.47,nan],[prb:nan,3,3,5,14,20,134.86,12.7,8.6,6.46,-22.92,nan],[prp:-22.92,3,3...</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -913,34 +885,62 @@
       <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>64265165900006</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>64165163290002</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>64165163150005</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DEV032399</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>NV: what is the RC?</t>
-        </is>
-      </c>
+          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>mst_devices_ELS-MST ELS device presence</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -953,56 +953,35 @@
       <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" t="n">
-        <v>64265165900007</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>64165163290001</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>DEV032399</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,8,6,16,8,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,9,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,10,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,11,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,7,16,12,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,13,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,14,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,15,64,0,31.89,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NV: What is the RC?
+Harness SS issue - MGMT to CSM </t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1021,10 +1000,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>64265165900008</v>
+        <v>64265165900007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1032,21 +1011,15 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>64165163290003</v>
+        <v>64165163290001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>64165163150002</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
           <t>FAIL</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -1062,10 +1035,14 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,8,6,16,8,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,9,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,10,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,6,16,11,63,0,31.86,-327.68,-1,-100],[eocl:-1.0,8,7,16,12,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,13,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,14,64,0,31.89,-327.68,-1,-100],[eocl:-1.0,8,7,16,15,64,0,31.89,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1079,34 +1056,58 @@
       <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>64265165900008</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>64165163290003</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>64165163150002</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DEV032399</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
+          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>NV: what is the RC?</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1119,40 +1120,34 @@
       <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>64165163330007</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>64165163290005</v>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>DEV032399</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NV: what is the RC?</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1164,6 +1159,74 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>64165163330007</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>64165163290005</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>64165163150004</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DEV032399</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-19.91,9,2,17,8,67,124.56,12.86,8.09,6.6,-19.91,nan],[prb:nan,9,2,17,8,67,124.56,12.86,8.09,6.6,-19.91,nan],[prb:nan,9,2,17,9,67,124.56,12.89,8.06,6.73,-2.38,nan],[prb:nan,9,2,17,10,67,124.56,13.01,7.94,6.73,-2.01,nan],[prb:nan,9,2,17,11,67,124.56,12.89,8.06,6.6,-2.11,nan]</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
